--- a/docs/KKBOX接腳定義.xlsx
+++ b/docs/KKBOX接腳定義.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Len\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Len\Documents\1.GitHub\kkbox\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834C847F-3A95-44CD-B784-572026930299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8210172-5F99-424C-B82D-EE20B925CAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -111,9 +111,6 @@
   <si>
     <t>Gyro pitch</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>外部端子 / 模組標示</t>
   </si>
   <si>
     <t>Pin 腳編號</t>
@@ -314,6 +311,10 @@
   </si>
   <si>
     <t>3,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外部端子 / 模組標示</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -777,16 +778,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="5" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -800,7 +801,7 @@
         <v>21</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -828,7 +829,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -842,7 +843,7 @@
         <v>32</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -856,7 +857,7 @@
         <v>26</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -870,7 +871,7 @@
         <v>27</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -884,12 +885,12 @@
         <v>28</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9" s="11">
         <v>8</v>
@@ -898,12 +899,12 @@
         <v>23</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="11">
         <v>9</v>
@@ -917,7 +918,7 @@
     </row>
     <row r="11" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11" s="11">
         <v>10</v>
@@ -940,7 +941,7 @@
         <v>14</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -954,7 +955,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -968,7 +969,7 @@
         <v>12</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -982,7 +983,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -996,7 +997,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1010,7 +1011,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1024,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1038,7 +1039,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1052,12 +1053,12 @@
         <v>7</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" s="11">
         <v>4</v>
@@ -1066,12 +1067,12 @@
         <v>16</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>17</v>
@@ -1080,12 +1081,12 @@
         <v>21</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B23" s="11">
         <v>5</v>
@@ -1094,12 +1095,12 @@
         <v>17</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B24" s="11">
         <v>3</v>
@@ -1108,12 +1109,12 @@
         <v>15</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" s="11">
         <v>14</v>
@@ -1122,18 +1123,18 @@
         <v>29</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>19</v>
